--- a/output/pdf_financials_xlsx/LMS.xlsx
+++ b/output/pdf_financials_xlsx/LMS.xlsx
@@ -5801,46 +5801,46 @@
         <v>0.150379</v>
       </c>
       <c r="D92" s="3" t="n">
+        <v>0.150379</v>
+      </c>
+      <c r="E92" s="3" t="n">
         <v>0.769773</v>
       </c>
-      <c r="E92" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.888462</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.807611</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.740856</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.335671</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.820628</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.894113</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.749826</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.271038</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.271038</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.80286</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.117611</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.117611</v>
       </c>
     </row>
     <row r="93">
@@ -7263,7 +7263,7 @@
         <v>-2.26349</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.080486</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>5.055597</v>
@@ -10106,7 +10106,11 @@
           <t>Share-based payment reserves (note 8) 3,156,465</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -11896,7 +11900,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -13020,7 +13028,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -13962,7 +13974,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -14244,7 +14260,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -15210,7 +15230,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16266,7 +16290,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -16840,7 +16868,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -17816,7 +17848,11 @@
           <t>Reserves (Note 5) 888,462</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -18982,7 +19018,11 @@
           <t>Reserves 820,849</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -27850,7 +27890,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LMS.xlsx
+++ b/output/pdf_financials_xlsx/LMS.xlsx
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001903</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003925</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016024</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003661</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.00115</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001036</v>
       </c>
     </row>
     <row r="13">
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.451053</v>
+        <v>-0.44915</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.178159</v>
+        <v>-2.174234</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.00893</v>
+        <v>-0.992906</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.759177</v>
+        <v>-0.762838</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-5.278229</v>
@@ -1984,10 +1984,10 @@
         <v>-1.075404</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.176654</v>
+        <v>-2.177804</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.260284</v>
+        <v>-1.26132</v>
       </c>
     </row>
     <row r="28">
@@ -2059,16 +2059,16 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.451053</v>
+        <v>-0.44915</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.178159</v>
+        <v>-2.174234</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.00893</v>
+        <v>-0.992906</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.759177</v>
+        <v>-0.762838</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-5.278229</v>
@@ -2098,10 +2098,10 @@
         <v>-1.036987</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.157128</v>
+        <v>-2.158278</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.258655</v>
+        <v>-1.259691</v>
       </c>
     </row>
     <row r="30">
@@ -2363,13 +2363,13 @@
         <v>2.688011</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.026536</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.705583</v>
+        <v>0.000301</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005786</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.085908</v>
@@ -2381,7 +2381,7 @@
         <v>0.838013</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.088793</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.858197</v>
@@ -2477,13 +2477,13 @@
         <v>2.688011</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.026536</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.705583</v>
+        <v>0.000301</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.005786</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.085908</v>
@@ -2495,7 +2495,7 @@
         <v>0.838013</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.088793</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.858197</v>
@@ -3161,13 +3161,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.026536</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005786</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3179,7 +3179,7 @@
         <v>0.113265</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.133617</v>
+        <v>0.044824</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.050753</v>
@@ -13222,7 +13222,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -51878,7 +51878,7 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
@@ -52556,7 +52556,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -55070,7 +55070,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
